--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 78 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 77 clubs short</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3555,8 +3555,8 @@
       <c r="T28" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U28" s="9" t="n">
-        <v>0</v>
+      <c r="U28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V28" s="9" t="n">
         <v>0</v>
@@ -3615,13 +3615,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" s="9" t="n">
         <v>0</v>
@@ -4645,13 +4645,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9304,8 +9304,8 @@
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -10664,7 +10664,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10678,13 +10678,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10722,8 +10722,8 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>3</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10914,8 +10914,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>3</v>
+      <c r="P100" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q100" s="10" t="n">
         <v>2</v>
@@ -11286,13 +11286,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
@@ -11334,7 +11334,7 @@
         <v>4</v>
       </c>
       <c r="W104" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X104" s="10" t="n">
         <v>5</v>
@@ -13197,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -14854,7 +14854,7 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14909,8 +14909,8 @@
       <c r="T140" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U140" s="9" t="n">
-        <v>0</v>
+      <c r="U140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V140" s="9" t="n">
         <v>1</v>
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="P145" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q145" s="9" t="n">
         <v>0</v>
@@ -15464,13 +15464,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>4</v>
       </c>
       <c r="W146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>7</v>
@@ -20393,7 +20393,7 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -20822,13 +20822,13 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -21053,7 +21053,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1646,7 +1650,11 @@
       <c r="AB9" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr"/>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2355,7 +2363,11 @@
       <c r="AB16" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC16" s="4" t="inlineStr"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3579,7 +3591,11 @@
       <c r="AB28" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3991,7 +4007,11 @@
       <c r="AB32" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -8400,7 +8420,11 @@
       <c r="AB75" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -9418,7 +9442,11 @@
       <c r="AB85" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9826,7 +9854,11 @@
       <c r="AB89" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC89" s="4" t="inlineStr"/>
+      <c r="AC89" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -9927,7 +9959,11 @@
       <c r="AB90" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10133,7 +10169,11 @@
       <c r="AB92" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC92" s="4" t="inlineStr"/>
+      <c r="AC92" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -14224,7 +14264,11 @@
       <c r="AB133" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14325,7 +14369,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14933,7 +14981,11 @@
       <c r="AB140" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC140" s="4" t="inlineStr"/>
+      <c r="AC140" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -18612,7 +18664,11 @@
       <c r="AB177" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC177" s="4" t="inlineStr"/>
+      <c r="AC177" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 77 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 71 clubs short</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W27" s="9" t="n">
         <v>0</v>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>1</v>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7989,8 +7989,8 @@
       <c r="S71" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T71" s="9" t="n">
-        <v>0</v>
+      <c r="T71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U71" s="9" t="n">
         <v>0</v>
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8648,7 +8648,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8718,8 +8718,8 @@
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9126,8 +9126,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -12302,7 +12302,7 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -12372,8 +12372,8 @@
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA114" s="10" t="n">
         <v>1</v>
@@ -12797,7 +12797,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12867,8 +12867,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -14696,7 +14696,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14766,8 +14766,8 @@
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA138" s="10" t="n">
         <v>1</v>
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15359,8 +15359,8 @@
       <c r="T144" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U144" s="9" t="n">
-        <v>0</v>
+      <c r="U144" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V144" s="9" t="n">
         <v>0</v>
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16760,8 +16760,8 @@
       <c r="Y158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z158" s="9" t="n">
-        <v>0</v>
+      <c r="Z158" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA158" s="10" t="n">
         <v>1</v>
@@ -16830,7 +16830,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" s="6" t="n">
         <v>10</v>
@@ -17793,13 +17793,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
@@ -17837,8 +17837,8 @@
       <c r="U169" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V169" s="9" t="n">
-        <v>3</v>
+      <c r="V169" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W169" s="9" t="n">
         <v>0</v>
@@ -20713,7 +20713,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20779,7 +20779,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -20977,7 +20977,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -21010,7 +21010,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -21109,7 +21109,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -21142,7 +21142,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 71 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 37 clubs short</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -2049,8 +2049,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2144,8 +2144,8 @@
       <c r="W14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X14" s="9" t="n">
-        <v>0</v>
+      <c r="X14" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2349,7 +2349,7 @@
         <v>1</v>
       </c>
       <c r="X16" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y16" s="9" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2643,8 +2643,8 @@
       <c r="S19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T19" s="9" t="n">
-        <v>0</v>
+      <c r="T19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U19" s="9" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2762,8 +2762,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3888,7 +3888,7 @@
         <v>0</v>
       </c>
       <c r="X31" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y31" s="9" t="n">
         <v>0</v>
@@ -4134,7 +4134,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4186,8 +4186,8 @@
       <c r="S34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T34" s="9" t="n">
-        <v>0</v>
+      <c r="T34" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U34" s="9" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4410,8 +4410,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4490,8 +4490,8 @@
       <c r="R37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>1</v>
+      <c r="S37" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T37" s="10" t="n">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>0</v>
       </c>
       <c r="X40" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y40" s="9" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5541,8 +5541,8 @@
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5572,7 +5572,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5642,8 +5642,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5747,8 +5747,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5852,8 +5852,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6054,8 +6054,8 @@
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6339,7 +6339,7 @@
         <v>2</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6781,8 +6781,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6960,7 +6960,7 @@
         <v>2</v>
       </c>
       <c r="R61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="9" t="n">
         <v>0</v>
@@ -7434,13 +7434,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>62</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="W66" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X66" s="10" t="n">
         <v>6</v>
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7902,8 +7902,8 @@
       <c r="Y70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z70" s="9" t="n">
-        <v>0</v>
+      <c r="Z70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA70" s="10" t="n">
         <v>1</v>
@@ -7937,7 +7937,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>1</v>
@@ -8007,8 +8007,8 @@
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -8240,7 +8240,7 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8310,8 +8310,8 @@
       <c r="Y74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z74" s="9" t="n">
-        <v>0</v>
+      <c r="Z74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA74" s="10" t="n">
         <v>1</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8617,8 +8617,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8749,7 +8749,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8819,8 +8819,8 @@
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="9" t="n">
-        <v>0</v>
+      <c r="Z79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8850,7 +8850,7 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K80" s="4" t="n">
         <v>0</v>
@@ -8920,8 +8920,8 @@
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
@@ -8965,13 +8965,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9538,8 +9538,8 @@
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="9" t="n">
-        <v>0</v>
+      <c r="Z86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9744,8 +9744,8 @@
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -10142,8 +10142,8 @@
       <c r="S92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T92" s="9" t="n">
-        <v>0</v>
+      <c r="T92" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U92" s="9" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10265,8 +10265,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10502,7 +10502,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10572,8 +10572,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10809,7 +10809,7 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10879,8 +10879,8 @@
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
@@ -11015,7 +11015,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11085,8 +11085,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11807,7 +11807,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11877,8 +11877,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12217,13 +12217,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12261,8 +12261,8 @@
       <c r="U113" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>3</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12500,7 +12500,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12570,8 +12570,8 @@
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
@@ -12995,7 +12995,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13065,8 +13065,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13094,7 +13094,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13164,8 +13164,8 @@
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z122" s="9" t="n">
-        <v>0</v>
+      <c r="Z122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA122" s="10" t="n">
         <v>1</v>
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13702,13 +13702,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13758,8 +13758,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13927,7 +13927,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>1</v>
@@ -14609,13 +14609,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>7</v>
@@ -15345,7 +15345,7 @@
         </is>
       </c>
       <c r="P144" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>0</v>
@@ -15756,7 +15756,7 @@
         <v>1</v>
       </c>
       <c r="U148" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V148" s="10" t="n">
         <v>4</v>
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>1</v>
@@ -17383,7 +17383,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17453,8 +17453,8 @@
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17552,8 +17552,8 @@
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="9" t="n">
-        <v>0</v>
+      <c r="Z166" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA166" s="10" t="n">
         <v>1</v>
@@ -17750,8 +17750,8 @@
       <c r="Y168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z168" s="9" t="n">
-        <v>0</v>
+      <c r="Z168" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA168" s="9" t="n">
         <v>0</v>
@@ -18177,7 +18177,7 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18226,8 +18226,8 @@
       <c r="R173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S173" s="9" t="n">
-        <v>1</v>
+      <c r="S173" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T173" s="9" t="n">
         <v>0</v>
@@ -18282,7 +18282,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18352,8 +18352,8 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18453,8 +18453,8 @@
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="9" t="n">
-        <v>0</v>
+      <c r="Z175" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -19276,7 +19276,7 @@
         <v>0</v>
       </c>
       <c r="X183" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y183" s="9" t="n">
         <v>0</v>
@@ -19380,8 +19380,8 @@
       <c r="W184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X184" s="9" t="n">
-        <v>2</v>
+      <c r="X184" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
@@ -19526,7 +19526,7 @@
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19596,8 +19596,8 @@
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="9" t="n">
-        <v>0</v>
+      <c r="Z186" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA186" s="10" t="n">
         <v>1</v>
@@ -19631,7 +19631,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19701,8 +19701,8 @@
       <c r="Y187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="9" t="n">
-        <v>0</v>
+      <c r="Z187" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA187" s="10" t="n">
         <v>1</v>
@@ -19736,7 +19736,7 @@
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -19800,14 +19800,14 @@
       <c r="W188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X188" s="9" t="n">
-        <v>0</v>
+      <c r="X188" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z188" s="9" t="n">
-        <v>0</v>
+      <c r="Z188" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA188" s="10" t="n">
         <v>1</v>
@@ -20350,7 +20350,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -20383,7 +20383,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -20416,7 +20416,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -20482,7 +20482,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -20515,7 +20515,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -20581,7 +20581,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -20647,7 +20647,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -20713,7 +20713,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20746,7 +20746,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -20779,7 +20779,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -20812,7 +20812,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -20845,7 +20845,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20878,7 +20878,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -20911,7 +20911,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -20944,7 +20944,7 @@
         <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -20977,13 +20977,13 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -21010,7 +21010,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -21043,7 +21043,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -21340,7 +21340,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -21406,7 +21406,7 @@
         <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -21439,7 +21439,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 14 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1068,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1274,13 +1274,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -2193,13 +2193,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>1</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2943,11 +2943,11 @@
       <c r="R22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+      <c r="S22" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3631,13 +3631,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="6" t="n">
         <v>10</v>
@@ -3773,8 +3773,8 @@
       <c r="T30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U30" s="9" t="n">
-        <v>0</v>
+      <c r="U30" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V30" s="10" t="n">
         <v>4</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4496,8 +4496,8 @@
       <c r="T37" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
+      <c r="U37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V37" s="9" t="n">
         <v>2</v>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -4871,13 +4871,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5810,11 +5810,11 @@
         </is>
       </c>
       <c r="M50" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
@@ -5855,8 +5855,8 @@
       <c r="Z50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA50" s="9" t="n">
-        <v>0</v>
+      <c r="AA50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="inlineStr"/>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5931,13 +5931,13 @@
         <v>0</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
+      <c r="U51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V51" s="9" t="n">
         <v>2</v>
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7840,13 +7840,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7887,8 +7887,8 @@
       <c r="V70" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W70" s="9" t="n">
-        <v>3</v>
+      <c r="W70" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X70" s="10" t="n">
         <v>7</v>
@@ -8252,13 +8252,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -9503,7 +9503,7 @@
         </is>
       </c>
       <c r="P86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q86" s="9" t="n">
         <v>0</v>
@@ -9608,10 +9608,10 @@
         </is>
       </c>
       <c r="P87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>0</v>
@@ -9888,13 +9888,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9924,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T90" s="9" t="n">
         <v>0</v>
@@ -9993,13 +9993,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10203,17 +10203,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-8</v>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10230,7 +10230,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>1</v>
@@ -10514,13 +10514,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10615,13 +10615,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11271,8 +11271,8 @@
       <c r="U103" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V103" s="9" t="n">
-        <v>2</v>
+      <c r="V103" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -12401,7 +12401,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12447,8 +12447,8 @@
       <c r="Q115" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R115" s="9" t="n">
-        <v>1</v>
+      <c r="R115" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S115" s="9" t="n">
         <v>1</v>
@@ -12613,13 +12613,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -13207,13 +13207,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
@@ -13306,13 +13306,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13999,13 +13999,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14508,13 +14508,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -15417,17 +15417,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L145" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -15462,7 +15462,7 @@
         <v>1</v>
       </c>
       <c r="V145" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15615,13 +15615,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15839,8 +15839,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P149" s="9" t="n">
-        <v>3</v>
+      <c r="P149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q149" s="10" t="n">
         <v>2</v>
@@ -15855,7 +15855,7 @@
         <v>1</v>
       </c>
       <c r="U149" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V149" s="10" t="n">
         <v>4</v>
@@ -16110,13 +16110,13 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J152" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K152" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L152" s="7" t="inlineStr">
         <is>
@@ -16506,13 +16506,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F158" s="6" t="n">
         <v>10</v>
@@ -16748,8 +16748,8 @@
       <c r="U158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="10" t="n">
-        <v>4</v>
+      <c r="V158" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W158" s="9" t="n">
         <v>0</v>
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16803,13 +16803,13 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J159" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
@@ -16850,8 +16850,8 @@
       <c r="V159" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W159" s="9" t="n">
-        <v>3</v>
+      <c r="W159" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X159" s="10" t="n">
         <v>7</v>
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16902,17 +16902,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L160" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-4</v>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -16940,8 +16940,8 @@
       <c r="S160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T160" s="9" t="n">
-        <v>0</v>
+      <c r="T160" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U160" s="9" t="n">
         <v>0</v>
@@ -17100,13 +17100,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17199,13 +17199,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         </is>
       </c>
       <c r="E164" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F164" s="6" t="n">
         <v>10</v>
@@ -17298,13 +17298,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17342,8 +17342,8 @@
       <c r="U164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V164" s="9" t="n">
-        <v>2</v>
+      <c r="V164" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -17496,13 +17496,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -17622,7 +17622,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -17892,13 +17892,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -17940,7 +17940,7 @@
         <v>4</v>
       </c>
       <c r="W170" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X170" s="10" t="n">
         <v>7</v>
@@ -18290,13 +18290,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         </is>
       </c>
       <c r="P179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q179" s="9" t="n">
         <v>0</v>
@@ -18940,7 +18940,7 @@
         <v>0</v>
       </c>
       <c r="S180" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T180" s="10" t="n">
         <v>1</v>
@@ -19219,13 +19219,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
@@ -19429,13 +19429,13 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J185" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K185" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
@@ -19534,13 +19534,13 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L186" s="7" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>0</v>
       </c>
       <c r="V186" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W186" s="9" t="n">
         <v>0</v>
@@ -20055,13 +20055,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q191" s="9" t="n">
         <v>1</v>
@@ -20515,7 +20515,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -20581,7 +20581,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -20614,7 +20614,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -20680,7 +20680,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -20692,7 +20692,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -20812,7 +20812,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -21010,7 +21010,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21076,7 +21076,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -21256,7 +21256,7 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -21274,7 +21274,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -21340,7 +21340,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -21355,7 +21355,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -21373,7 +21373,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/84/inyear.xlsx
+++ b/docs/d/84/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 13 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 13 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 36 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 36 clubs short</t>
         </is>
       </c>
     </row>
@@ -1480,13 +1480,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>2</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2298,13 +2298,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>1</v>
@@ -2346,7 +2346,7 @@
         <v>4</v>
       </c>
       <c r="W16" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X16" s="10" t="n">
         <v>6</v>
@@ -2999,7 +2999,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3013,13 +3013,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3057,8 +3057,8 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>3</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>4</v>
       </c>
       <c r="W24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>5</v>
@@ -3316,13 +3316,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3631,13 +3631,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
@@ -5283,13 +5283,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6435,10 +6435,10 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q56" s="10" t="n">
         <v>2</v>
-      </c>
-      <c r="Q56" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6509,17 +6509,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6554,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6719,17 +6719,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7026,13 +7026,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -7052,8 +7052,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P62" s="9" t="n">
-        <v>3</v>
+      <c r="P62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q62" s="10" t="n">
         <v>2</v>
@@ -7113,7 +7113,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7127,13 +7127,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7171,8 +7171,8 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="9" t="n">
-        <v>3</v>
+      <c r="V63" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7432,13 +7432,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7638,13 +7638,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7875,8 +7875,8 @@
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="9" t="n">
-        <v>1</v>
+      <c r="S70" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T70" s="10" t="n">
         <v>1</v>
@@ -8036,7 +8036,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8050,13 +8050,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8094,11 +8094,11 @@
       <c r="U72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="9" t="n">
-        <v>3</v>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>5</v>
@@ -8454,13 +8454,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8761,13 +8761,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8797,19 +8797,19 @@
         <v>0</v>
       </c>
       <c r="S79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V79" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X79" s="10" t="n">
         <v>6</v>
@@ -9476,13 +9476,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9874,7 +9874,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9926,8 +9926,8 @@
       <c r="S90" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T90" s="9" t="n">
-        <v>0</v>
+      <c r="T90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U90" s="9" t="n">
         <v>0</v>
@@ -9993,13 +9993,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
@@ -10041,7 +10041,7 @@
         <v>4</v>
       </c>
       <c r="W91" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X91" s="10" t="n">
         <v>6</v>
@@ -10203,13 +10203,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10350,7 +10350,7 @@
         <v>1</v>
       </c>
       <c r="U94" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V94" s="9" t="n">
         <v>0</v>
@@ -10514,13 +10514,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10716,13 +10716,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -11013,7 +11013,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11062,8 +11062,8 @@
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S101" s="9" t="n">
-        <v>1</v>
+      <c r="S101" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T101" s="10" t="n">
         <v>1</v>
@@ -11227,13 +11227,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
@@ -11425,13 +11425,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>5</v>
@@ -11510,7 +11510,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11524,13 +11524,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
@@ -11568,8 +11568,8 @@
       <c r="U106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="9" t="n">
-        <v>3</v>
+      <c r="V106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
@@ -11920,13 +11920,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X110" s="9" t="n">
         <v>1</v>
@@ -12220,10 +12220,10 @@
         <v>7</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -12514,13 +12514,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12643,7 +12643,7 @@
         <v>1</v>
       </c>
       <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
@@ -12651,8 +12651,8 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
@@ -13292,7 +13292,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13306,17 +13306,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L124" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13353,8 +13353,8 @@
       <c r="V124" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>2</v>
+      <c r="W124" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X124" s="9" t="n">
         <v>2</v>
@@ -13900,17 +13900,17 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M130" s="8" t="n">
@@ -13945,7 +13945,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -14098,13 +14098,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14235,8 +14235,8 @@
       <c r="S133" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
@@ -14284,7 +14284,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14339,8 +14339,8 @@
       <c r="T134" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U134" s="9" t="n">
-        <v>0</v>
+      <c r="U134" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V134" s="10" t="n">
         <v>4</v>
@@ -14508,13 +14508,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -15219,13 +15219,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -15318,13 +15318,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>0</v>
       </c>
       <c r="Q144" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R144" s="9" t="n">
         <v>0</v>
@@ -15362,11 +15362,11 @@
       <c r="U144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W144" s="9" t="n">
-        <v>0</v>
+      <c r="V144" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W144" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X144" s="9" t="n">
         <v>0</v>
@@ -15651,7 +15651,7 @@
         <v>0</v>
       </c>
       <c r="S147" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T147" s="10" t="n">
         <v>1</v>
@@ -15813,13 +15813,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>1</v>
       </c>
       <c r="U149" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V149" s="10" t="n">
         <v>4</v>
@@ -16902,13 +16902,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>0</v>
       </c>
       <c r="S162" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T162" s="9" t="n">
         <v>0</v>
@@ -17793,13 +17793,13 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J169" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K169" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="E170" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F170" s="6" t="n">
         <v>10</v>
@@ -17892,13 +17892,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>40</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
@@ -17939,8 +17939,8 @@
       <c r="V170" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W170" s="9" t="n">
-        <v>2</v>
+      <c r="W170" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X170" s="10" t="n">
         <v>7</v>
@@ -18290,13 +18290,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18698,13 +18698,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -20746,7 +20746,7 @@
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -20761,7 +20761,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -20779,7 +20779,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -20812,13 +20812,13 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -20878,7 +20878,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -20944,7 +20944,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -20977,7 +20977,7 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -21010,7 +21010,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21076,7 +21076,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -21109,7 +21109,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -21124,7 +21124,7 @@
         <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -21157,7 +21157,7 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -21175,13 +21175,13 @@
         <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -21406,13 +21406,13 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
